--- a/originales/respuestas/2025/01. Calificadas/bucle p11/Alcaldía Local De Engativá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p11/Alcaldía Local De Engativá.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\Desktop\Respuesta\bucle p11\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Unidades compartidas\VDLab\2025\2. Componente IIP\Etapa 3. Calificación\02. Calificadas\bucle p11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835AA3E6-381D-42BB-9DC4-395F5A418A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4B6789-5730-443E-87B7-F3255433D9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91DD58F3-AD5F-4CAB-A83E-F794006E5839}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="11625" windowHeight="15585" xr2:uid="{91DD58F3-AD5F-4CAB-A83E-F794006E5839}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -665,7 +665,7 @@
         <v>25</v>
       </c>
       <c r="P2" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>27</v>
